--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,53 +794,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127830739</v>
+        <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>99112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodberget, Jmt</t>
+          <t>Storkojan, Storkojan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521830</v>
+        <v>522313</v>
       </c>
       <c r="R3" t="n">
-        <v>6948946</v>
+        <v>6949414</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,64 +879,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127830762</v>
+        <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>102871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>223037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybodberget, Jmt</t>
+          <t>Storkojan, Storkojan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522138</v>
+        <v>522313</v>
       </c>
       <c r="R4" t="n">
-        <v>6947688</v>
+        <v>6949414</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,26 +976,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127830757</v>
+        <v>127830739</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>57364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,37 +999,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybodberget, Jmt</t>
+          <t>Gammalbodberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521733</v>
+        <v>521830</v>
       </c>
       <c r="R5" t="n">
-        <v>6946724</v>
+        <v>6948946</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1058,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1093,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1132,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127830759</v>
+        <v>127830762</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1167,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521734</v>
+        <v>522138</v>
       </c>
       <c r="R6" t="n">
-        <v>6946715</v>
+        <v>6947688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127830688</v>
+        <v>127830757</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1278,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519908</v>
+        <v>521733</v>
       </c>
       <c r="R7" t="n">
-        <v>6945195</v>
+        <v>6946724</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1315,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sonja Jederlund</t>
+          <t>Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1354,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127830687</v>
+        <v>127830759</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,13 +1361,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520804</v>
+        <v>521734</v>
       </c>
       <c r="R8" t="n">
-        <v>6945042</v>
+        <v>6946715</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1426,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sonja Jederlund</t>
+          <t>Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1465,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127830749</v>
+        <v>127830688</v>
       </c>
       <c r="B9" t="n">
         <v>80432</v>
@@ -1500,13 +1472,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518918</v>
+        <v>519908</v>
       </c>
       <c r="R9" t="n">
-        <v>6944789</v>
+        <v>6945195</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,22 +1502,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1537,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
+          <t>Sonja Jederlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1576,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127830750</v>
+        <v>127830687</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1583,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>520804</v>
       </c>
       <c r="R10" t="n">
-        <v>6944788</v>
+        <v>6945042</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1613,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,10 +1648,232 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127830749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nybodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518918</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6944789</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Agnes  Blomgren</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127830750</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nybodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518812</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6944788</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Agnes  Blomgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126058903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350027</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349931</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830739</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830762</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830759</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830688</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830687</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830749</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,8 +1933,26 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,53 +804,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127830739</v>
+        <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>99191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammalbodberget, Jmt</t>
+          <t>Storkojan, Storkojan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521830</v>
+        <v>522313</v>
       </c>
       <c r="R3" t="n">
-        <v>6948946</v>
+        <v>6949414</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,69 +889,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830739</t>
+          <t>https://artportalen.se/Sighting/135350027</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127830762</v>
+        <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>102954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>223037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybodberget, Jmt</t>
+          <t>Storkojan, Storkojan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522138</v>
+        <v>522313</v>
       </c>
       <c r="R4" t="n">
-        <v>6947688</v>
+        <v>6949414</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,31 +991,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830762</t>
+          <t>https://artportalen.se/Sighting/135349931</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127830757</v>
+        <v>127830739</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>57364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,37 +1019,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102954</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybodberget, Jmt</t>
+          <t>Gammalbodberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521733</v>
+        <v>521830</v>
       </c>
       <c r="R5" t="n">
-        <v>6946724</v>
+        <v>6948946</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1078,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1113,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1151,13 +1123,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830757</t>
+          <t>https://artportalen.se/Sighting/127830739</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127830759</v>
+        <v>127830762</v>
       </c>
       <c r="B6" t="n">
         <v>80432</v>
@@ -1192,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521734</v>
+        <v>522138</v>
       </c>
       <c r="R6" t="n">
-        <v>6946715</v>
+        <v>6947688</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,13 +1239,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830759</t>
+          <t>https://artportalen.se/Sighting/127830762</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127830688</v>
+        <v>127830757</v>
       </c>
       <c r="B7" t="n">
         <v>80432</v>
@@ -1308,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519908</v>
+        <v>521733</v>
       </c>
       <c r="R7" t="n">
-        <v>6945195</v>
+        <v>6946724</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1343,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sonja Jederlund</t>
+          <t>Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1383,16 +1355,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830688</t>
+          <t>https://artportalen.se/Sighting/127830757</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127830687</v>
+        <v>127830759</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1424,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520804</v>
+        <v>521734</v>
       </c>
       <c r="R8" t="n">
-        <v>6945042</v>
+        <v>6946715</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sonja Jederlund</t>
+          <t>Agnes  Blomgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1499,13 +1471,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830687</t>
+          <t>https://artportalen.se/Sighting/127830759</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127830749</v>
+        <v>127830688</v>
       </c>
       <c r="B9" t="n">
         <v>80432</v>
@@ -1540,13 +1512,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518918</v>
+        <v>519908</v>
       </c>
       <c r="R9" t="n">
-        <v>6944789</v>
+        <v>6945195</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,22 +1542,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,7 +1577,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Agnes  Blomgren</t>
+          <t>Sonja Jederlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1615,16 +1587,16 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830749</t>
+          <t>https://artportalen.se/Sighting/127830688</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127830750</v>
+        <v>127830687</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,13 +1628,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518812</v>
+        <v>520804</v>
       </c>
       <c r="R10" t="n">
-        <v>6944788</v>
+        <v>6945042</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,22 +1658,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,15 +1693,247 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830687</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127830749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nybodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>518918</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6944789</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Agnes  Blomgren</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830749</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127830750</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nybodberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>518812</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6944788</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Agnes  Blomgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127830750</t>
         </is>
@@ -1746,6 +1950,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 571-2026 artfynd.xlsx
+++ b/artfynd/S 571-2026 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135350027</v>
       </c>
       <c r="B3" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135349931</v>
       </c>
       <c r="B4" t="n">
-        <v>102956</v>
+        <v>102975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
